--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_220_R22.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_220_R22.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2614</v>
+        <v>5.4693</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4408</v>
+        <v>4.6152</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8206</v>
+        <v>0.8542</v>
       </c>
       <c r="G2" t="n">
         <v>4.0428</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>1.198</v>
+        <v>0.4059</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1993</v>
+        <v>0.3736</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0013</v>
+        <v>0.0323</v>
       </c>
       <c r="V2" t="n">
         <v>0.7886</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0669</v>
+        <v>3.6343</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7988</v>
+        <v>2.2655</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2681</v>
+        <v>1.3689</v>
       </c>
       <c r="G3" t="n">
         <v>2.035</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8901</v>
+        <v>1.4576</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4812</v>
+        <v>0.9478</v>
       </c>
       <c r="U3" t="n">
-        <v>0.409</v>
+        <v>0.5098</v>
       </c>
       <c r="V3" t="n">
         <v>0.1418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0296</v>
+        <v>3.4171</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3977</v>
+        <v>2.7515</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6319</v>
+        <v>0.6656</v>
       </c>
       <c r="G4" t="n">
         <v>3.0151</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4494</v>
+        <v>-0.0619</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4481</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0013</v>
+        <v>0.0323</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9117</v>
+        <v>1.835</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4197</v>
+        <v>-1.8915</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3314</v>
+        <v>3.7265</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7459</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2659</v>
+        <v>1.1892</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6765</v>
+        <v>0.2047</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5894</v>
+        <v>0.9845</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4641</v>
+        <v>1.7852</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2222</v>
+        <v>-2.0049</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2419</v>
+        <v>3.7901</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6567</v>
+        <v>-0.035</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1849</v>
+        <v>-0.0048</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4718</v>
+        <v>-0.0303</v>
       </c>
       <c r="J6" t="n">
-        <v>0.521</v>
+        <v>-1.4037</v>
       </c>
       <c r="K6" t="n">
-        <v>0.521</v>
+        <v>-0.3795</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.0241</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1357</v>
+        <v>1.3686</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3361</v>
+        <v>0.3748</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4718</v>
+        <v>0.9939</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1116</v>
+        <v>0.1966</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2987</v>
+        <v>-0.3692</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4103</v>
+        <v>0.5658</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1005</v>
+        <v>1.5045</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.431</v>
+        <v>-2.1951</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5316</v>
+        <v>3.6996</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5426</v>
@@ -1000,13 +1000,13 @@
         <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1946</v>
+        <v>0.5985</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1019</v>
+        <v>0.134</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2965</v>
+        <v>0.4646</v>
       </c>
       <c r="V7" t="n">
         <v>2.1444</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8857</v>
+        <v>1.4017</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1892</v>
+        <v>0.1892</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3035</v>
+        <v>1.2125</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3987</v>
+        <v>0.6872</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0228</v>
+        <v>0.4261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4216</v>
+        <v>0.261</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4103</v>
+        <v>0.3228</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3564</v>
+        <v>0.3228</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0539</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0116</v>
+        <v>0.3644</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3792</v>
+        <v>0.1034</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6323</v>
+        <v>0.261</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5386</v>
+        <v>0.2506</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7943</v>
+        <v>0.0984</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2557</v>
+        <v>0.1522</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6946</v>
+        <v>1.1952</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2826</v>
+        <v>0.2222</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9772</v>
+        <v>0.973</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6872</v>
+        <v>0.6567</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4261</v>
+        <v>0.1849</v>
       </c>
       <c r="I9" t="n">
-        <v>0.261</v>
+        <v>0.4718</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3228</v>
+        <v>0.521</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3228</v>
+        <v>0.521</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3644</v>
+        <v>0.1357</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1034</v>
+        <v>-0.3361</v>
       </c>
       <c r="O9" t="n">
-        <v>0.261</v>
+        <v>0.4718</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4564</v>
+        <v>-0.1573</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3734</v>
+        <v>-0.2987</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.083</v>
+        <v>0.1415</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4218</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8305</v>
+        <v>-1.412</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2524</v>
+        <v>2.1605</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.035</v>
+        <v>-0.605</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0048</v>
+        <v>0.4959</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0303</v>
+        <v>-1.1009</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4037</v>
+        <v>-0.4333</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3795</v>
+        <v>0.4033</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0241</v>
+        <v>-0.8366</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3686</v>
+        <v>-0.1717</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3748</v>
+        <v>0.0926</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9939</v>
+        <v>-0.2643</v>
       </c>
       <c r="P10" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.6237</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.8556</v>
-      </c>
       <c r="S10" t="n">
-        <v>-1.1668</v>
+        <v>0.2427</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1949</v>
+        <v>0.181</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0281</v>
+        <v>0.0617</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6468</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3103</v>
+        <v>0.6498</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8838</v>
+        <v>2.9533</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1941</v>
+        <v>-2.3035</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.605</v>
+        <v>0.3987</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4959</v>
+        <v>-0.0228</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1009</v>
+        <v>0.4216</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4333</v>
+        <v>1.4103</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4033</v>
+        <v>0.3564</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8366</v>
+        <v>1.0539</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1717</v>
+        <v>-1.0116</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0926</v>
+        <v>-0.3792</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2643</v>
+        <v>-0.6323</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1955</v>
+        <v>0.3027</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2908</v>
+        <v>0.5583</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0953</v>
+        <v>-0.2557</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6468</v>
+        <v>-0.2836</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6468</v>
+        <v>-2.428</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2028</v>
+        <v>-0.9326</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3891</v>
+        <v>-0.9173</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1864</v>
+        <v>-0.0153</v>
       </c>
       <c r="G12" t="n">
         <v>2.2828</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1661</v>
+        <v>0.1041</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4402</v>
+        <v>0.0316</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2741</v>
+        <v>0.0725</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5361</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1687</v>
+        <v>-1.9328</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0716</v>
+        <v>-3.8357</v>
       </c>
       <c r="F13" t="n">
         <v>1.9029</v>
@@ -1468,10 +1468,10 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5386</v>
+        <v>-0.3027</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8215</v>
+        <v>-0.5856</v>
       </c>
       <c r="U13" t="n">
         <v>0.2829</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.7751</v>
+        <v>18.7752</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7403999999999975</v>
+        <v>0.7403999999999993</v>
       </c>
       <c r="F14" t="n">
         <v>18.035</v>
@@ -1519,13 +1519,13 @@
         <v>9.2012</v>
       </c>
       <c r="J14" t="n">
-        <v>8.9366</v>
+        <v>8.936599999999999</v>
       </c>
       <c r="K14" t="n">
         <v>3.3833</v>
       </c>
       <c r="L14" t="n">
-        <v>5.553399999999999</v>
+        <v>5.553399999999998</v>
       </c>
       <c r="M14" t="n">
         <v>1.9451</v>
@@ -1534,10 +1534,10 @@
         <v>-1.7026</v>
       </c>
       <c r="O14" t="n">
-        <v>3.648</v>
+        <v>3.648000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>1.159899999999999</v>
+        <v>1.1599</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.2369</v>
@@ -1546,13 +1546,13 @@
         <v>17.3965</v>
       </c>
       <c r="S14" t="n">
-        <v>4.225999999999999</v>
+        <v>4.226</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1818</v>
+        <v>1.1817</v>
       </c>
       <c r="U14" t="n">
-        <v>3.044299999999999</v>
+        <v>3.0444</v>
       </c>
       <c r="V14" t="n">
         <v>2.5076</v>
@@ -1561,7 +1561,7 @@
         <v>6.8586</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.351000000000001</v>
+        <v>-4.351</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9264</v>
+        <v>2.993</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9745</v>
+        <v>2.7386</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0481</v>
+        <v>0.2544</v>
       </c>
       <c r="G15" t="n">
         <v>2.3323</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3879</v>
+        <v>-0.3213</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0395</v>
+        <v>-0.1964</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4274</v>
+        <v>-0.125</v>
       </c>
       <c r="V15" t="n">
         <v>1.214</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.605</v>
+        <v>0.6327</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1187</v>
+        <v>1.1596</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4863</v>
+        <v>-0.527</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.658</v>
+        <v>2.0901</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0625</v>
+        <v>3.0706</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5955</v>
+        <v>-0.9804</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3428</v>
+        <v>3.3768</v>
       </c>
       <c r="K16" t="n">
-        <v>0.306</v>
+        <v>3.146</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0368</v>
+        <v>0.2308</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0008</v>
+        <v>-1.2866</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3684</v>
+        <v>-0.0755</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6323</v>
+        <v>-1.2112</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3352</v>
+        <v>0.0786</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.224</v>
+        <v>0.1024</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5592</v>
+        <v>-0.0237</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5997</v>
+        <v>0.4712</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3955</v>
+        <v>0.3546</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7958</v>
+        <v>0.1166</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0901</v>
+        <v>-0.658</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0706</v>
+        <v>-0.0625</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9804</v>
+        <v>-0.5955</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3768</v>
+        <v>0.3428</v>
       </c>
       <c r="K17" t="n">
-        <v>3.146</v>
+        <v>0.306</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2308</v>
+        <v>0.0368</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2866</v>
+        <v>-1.0008</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0755</v>
+        <v>-0.3684</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2112</v>
+        <v>-0.6323</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0457</v>
+        <v>0.2014</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3383</v>
+        <v>0.0119</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2926</v>
+        <v>0.1896</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1867</v>
+        <v>0.268</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2148</v>
+        <v>0.5687</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4015</v>
+        <v>-0.3007</v>
       </c>
       <c r="G18" t="n">
         <v>0.8388</v>
@@ -1858,13 +1858,13 @@
         <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9353</v>
+        <v>-0.4806</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7468</v>
+        <v>-0.393</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1885</v>
+        <v>-0.0876</v>
       </c>
       <c r="V18" t="n">
         <v>0.1418</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9176</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9674</v>
+        <v>-0.8495</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0498</v>
+        <v>0.2179</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6587</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1867</v>
+        <v>0.0993</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U19" t="n">
-        <v>0.112</v>
+        <v>0.2801</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3676</v>
+        <v>-1.2833</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2755</v>
+        <v>-1.1576</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0921</v>
+        <v>-0.1257</v>
       </c>
       <c r="G20" t="n">
         <v>0.6627</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2016</v>
+        <v>0.286</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U20" t="n">
-        <v>0.351</v>
+        <v>0.3174</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.011</v>
+        <v>-2.6727</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-3.3569</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4621</v>
+        <v>0.6842</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.348</v>
+        <v>-1.3842</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1573</v>
+        <v>-1.1199</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1907</v>
+        <v>-0.2643</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.39</v>
+        <v>-1.5055</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4636</v>
+        <v>-0.7191</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0736</v>
+        <v>-0.7863</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9581</v>
+        <v>0.1213</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6938</v>
+        <v>-0.4008</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2643</v>
+        <v>0.5221</v>
       </c>
       <c r="P21" t="n">
         <v>-0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>1.52</v>
+        <v>-0.8246</v>
       </c>
       <c r="T21" t="n">
-        <v>1.5059</v>
+        <v>-0.4597</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0141</v>
+        <v>-0.3648</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.719</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.5051</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.68</v>
+        <v>-2.7466</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1161</v>
+        <v>-1.3745</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4361</v>
+        <v>-1.3721</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.08</v>
+        <v>-1.348</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3301</v>
+        <v>-1.1573</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7499</v>
+        <v>-0.1907</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.2515</v>
+        <v>-0.39</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7156</v>
+        <v>-0.4636</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5359</v>
+        <v>0.0736</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1715</v>
+        <v>-0.9581</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3856</v>
+        <v>-0.6938</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.214</v>
+        <v>-0.2643</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9195</v>
+        <v>0.7844</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6326000000000001</v>
+        <v>0.6803</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2869</v>
+        <v>0.1041</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>-1.719</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.5051</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.083</v>
+        <v>-2.806</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7108</v>
+        <v>-3.6786</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6278</v>
+        <v>0.8726</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3842</v>
+        <v>-2.4769</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1199</v>
+        <v>-0.0444</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2643</v>
+        <v>-2.4325</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5055</v>
+        <v>-1.7439</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7191</v>
+        <v>0.5783</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7863</v>
+        <v>-2.3222</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1213</v>
+        <v>-0.733</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4008</v>
+        <v>-0.6227</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5221</v>
+        <v>-0.1103</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2349</v>
+        <v>-0.8472</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8136</v>
+        <v>-0.5972</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4213</v>
+        <v>-0.25</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2879</v>
+        <v>-2.933</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6804</v>
+        <v>-3.4699</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3925</v>
+        <v>0.5369</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1522</v>
+        <v>-2.08</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.366</v>
+        <v>-0.3301</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7862</v>
+        <v>-1.7499</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5764</v>
+        <v>-2.2515</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9005</v>
+        <v>-0.7156</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-1.5359</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5758</v>
+        <v>0.1715</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4655</v>
+        <v>0.3856</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1103</v>
+        <v>-0.214</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1357</v>
+        <v>-1.1725</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6247</v>
+        <v>-0.9865</v>
       </c>
       <c r="U24" t="n">
-        <v>0.489</v>
+        <v>-0.186</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4858</v>
+        <v>-3.6347</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.2684</v>
+        <v>-3.6804</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7826</v>
+        <v>0.0456</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4769</v>
+        <v>-2.1522</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0444</v>
+        <v>-1.366</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.4325</v>
+        <v>-0.7862</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.7439</v>
+        <v>-1.5764</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5783</v>
+        <v>-0.9005</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.3222</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.733</v>
+        <v>-0.5758</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6227</v>
+        <v>-0.4655</v>
       </c>
       <c r="O25" t="n">
         <v>-0.1103</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q25" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.527</v>
+        <v>-0.4826</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.187</v>
+        <v>-0.6247</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.34</v>
+        <v>0.1421</v>
       </c>
       <c r="V25" t="n">
-        <v>1.214</v>
+        <v>-0.5361</v>
       </c>
       <c r="W25" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.8868</v>
+        <v>-5.6459</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.6351</v>
+        <v>-4.7531</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2517</v>
+        <v>-0.8928</v>
       </c>
       <c r="G26" t="n">
         <v>-5.0476</v>
@@ -2482,13 +2482,13 @@
         <v>1.1598</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0016</v>
+        <v>-0.7606000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2513</v>
+        <v>-0.3692</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7503</v>
+        <v>-0.3914</v>
       </c>
       <c r="V26" t="n">
         <v>0.3943</v>
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-18.7753</v>
+        <v>-17.9889</v>
       </c>
       <c r="E27" t="n">
-        <v>-17.4991</v>
+        <v>-17.499</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.2762</v>
+        <v>-0.4901000000000002</v>
       </c>
       <c r="G27" t="n">
         <v>-10.8817</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.6806</v>
+        <v>-1.680599999999999</v>
       </c>
       <c r="I27" t="n">
         <v>-9.2012</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.945099999999999</v>
+        <v>-1.9451</v>
       </c>
       <c r="K27" t="n">
-        <v>1.7026</v>
+        <v>1.702599999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.6477</v>
+        <v>-3.647700000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-8.9366</v>
+        <v>-8.936599999999999</v>
       </c>
       <c r="N27" t="n">
         <v>-3.3832</v>
@@ -2560,13 +2560,13 @@
         <v>16.2368</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.2261</v>
+        <v>-3.439700000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-3.0444</v>
+        <v>-3.0443</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.1817</v>
+        <v>-0.3952000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-2.5076</v>
